--- a/data/trans_orig/KIDM_C_2_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/KIDM_C_2_R-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen mucho o muchísimo cansancio para disfrutar de las cosas que le gustan (autopercepción menor) en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores que tienen mucho o muchísimo cansancio para disfrutar de las cosas que le gustan (autopercepción menor) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4246</t>
+          <t>4435</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4499</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>641</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5485</t>
+          <t>5637</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,33%</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t>7972</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12255</t>
+          <t>11211</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23677</t>
+          <t>23525</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28533</t>
+          <t>28521</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>868</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7446</t>
+          <t>7662</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>926</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8330</t>
+          <t>8314</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3123</t>
+          <t>3185</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12698</t>
+          <t>12728</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>151867</t>
+          <t>151651</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>158330</t>
+          <t>158445</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>194370</t>
+          <t>194386</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>201751</t>
+          <t>201774</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>349315</t>
+          <t>349285</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>358890</t>
+          <t>358828</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3022</t>
+          <t>3654</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>595</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6209</t>
+          <t>6540</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>931</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7350</t>
+          <t>7461</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35730</t>
+          <t>35098</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46484</t>
+          <t>46153</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52127</t>
+          <t>52098</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>84095</t>
+          <t>83984</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>90566</t>
+          <t>90514</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2036</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10461</t>
+          <t>10493</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2850</t>
+          <t>2791</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12076</t>
+          <t>12392</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6680</t>
+          <t>6662</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19244</t>
+          <t>18912</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>200011</t>
+          <t>199979</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>208375</t>
+          <t>208436</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>260071</t>
+          <t>259755</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>269297</t>
+          <t>269356</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>463375</t>
+          <t>463707</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>475939</t>
+          <t>475957</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
